--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="74">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.237 Patch 1</t>
+    <t xml:space="preserve">EA 23.247</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t xml:space="preserve">タレット</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cocoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cocoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コクーン</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 17.1</t>
@@ -333,10 +342,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -352,10 +361,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -371,10 +380,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -390,10 +399,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -409,10 +418,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -428,10 +437,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -447,10 +456,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -466,10 +475,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -485,10 +494,10 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
@@ -504,10 +513,10 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
@@ -523,10 +532,10 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
@@ -542,10 +551,10 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -561,10 +570,10 @@
         <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -580,10 +589,10 @@
         <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
         <v>49</v>
@@ -593,6 +602,22 @@
       </c>
       <c r="G16"/>
       <c r="H16"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17"/>
+      <c r="H17"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.252</t>
+    <t xml:space="preserve">EA 23.260</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.260</t>
+    <t xml:space="preserve">EA 23.267</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.267</t>
+    <t xml:space="preserve">EA 23.281</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.281</t>
+    <t xml:space="preserve">EA 23.282 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.282 Patch 2</t>
+    <t xml:space="preserve">EA 23.287</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.287</t>
+    <t xml:space="preserve">EA 23.295</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="79">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.295</t>
+    <t xml:space="preserve">EA 23.307</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>
@@ -177,6 +177,15 @@
   </si>
   <si>
     <t xml:space="preserve">コクーン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">runner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ランナー</t>
   </si>
   <si>
     <t xml:space="preserve">Alpha 17.1</t>
@@ -348,10 +357,10 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -367,10 +376,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
@@ -386,10 +395,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
         <v>16</v>
@@ -405,10 +414,10 @@
         <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -424,10 +433,10 @@
         <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
@@ -443,10 +452,10 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
         <v>25</v>
@@ -462,10 +471,10 @@
         <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -481,10 +490,10 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -500,10 +509,10 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
         <v>34</v>
@@ -519,10 +528,10 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>37</v>
@@ -538,10 +547,10 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D13" t="s">
         <v>40</v>
@@ -557,10 +566,10 @@
         <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -576,10 +585,10 @@
         <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D15" t="s">
         <v>46</v>
@@ -595,10 +604,10 @@
         <v>48</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D16" t="s">
         <v>49</v>
@@ -614,10 +623,10 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>52</v>
@@ -627,6 +636,22 @@
       </c>
       <c r="G17"/>
       <c r="H17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" t="s">
+        <v>55</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18"/>
+      <c r="H18"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:H2"/>

--- a/Mod_Korean/Lang/KR/Game/Tactics.xlsx
+++ b/Mod_Korean/Lang/KR/Game/Tactics.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">_</t>
   </si>
   <si>
-    <t xml:space="preserve">EA 23.325</t>
+    <t xml:space="preserve">EA 23.338 Patch 2</t>
   </si>
   <si>
     <t xml:space="preserve">Disable</t>
